--- a/5/search/FY2_Missile3_results/best_solution.xlsx
+++ b/5/search/FY2_Missile3_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="B2" t="n">
-        <v>137.2</v>
+        <v>122</v>
       </c>
       <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
       <c r="E2" t="n">
-        <v>12000</v>
+        <v>10964.79567234289</v>
       </c>
       <c r="F2" t="n">
-        <v>302.4000000000001</v>
+        <v>364.7956723428947</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12000</v>
+        <v>10274.65945390482</v>
       </c>
       <c r="I2" t="n">
-        <v>-383.5999999999999</v>
+        <v>-325.3405460951756</v>
       </c>
       <c r="J2" t="n">
-        <v>1277.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.700000000000001</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
